--- a/VerveStacks_CAN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CAN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD0693ED-D680-42B8-A18E-AE772E96F125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3FE3F57-8558-4DEA-BE42-9B8923E33350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CAN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CAN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3FE3F57-8558-4DEA-BE42-9B8923E33350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DD8F6D9-0E75-4D5F-BA36-580577A7551A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CAN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CAN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DD8F6D9-0E75-4D5F-BA36-580577A7551A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2949C400-B9FC-4F03-80C8-23290BBE96A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CAN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CAN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2949C400-B9FC-4F03-80C8-23290BBE96A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BE59D69-5F51-429F-AB2F-2B75E9370F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CAN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CAN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BE59D69-5F51-429F-AB2F-2B75E9370F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4704D4B-12BF-4ACD-B14E-4C6540B9A878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CAN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CAN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4704D4B-12BF-4ACD-B14E-4C6540B9A878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{304E05E6-0C52-4583-9C4E-EB713BD04EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CAN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CAN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{304E05E6-0C52-4583-9C4E-EB713BD04EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B8D918E-CEB6-4ED6-801D-D4FAC475503D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CAN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CAN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B8D918E-CEB6-4ED6-801D-D4FAC475503D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DAB0B58-292F-4B45-AC5C-A20F2E4E725C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
